--- a/backend/wp_templates/D/D7 合同负债.xlsx
+++ b/backend/wp_templates/D/D7 合同负债.xlsx
@@ -10565,7 +10565,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="14">
-        <f>C12+D12-E12</f>
+        <f>C12-D12+E12</f>
         <v>0</v>
       </c>
       <c r="G12" s="9"/>
@@ -10581,7 +10581,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="14">
-        <f t="shared" ref="F13:F14" si="0">C13+D13-E13</f>
+        <f t="shared" ref="F13:F14" si="0">C13-D13+E13</f>
         <v>0</v>
       </c>
       <c r="G13" s="11"/>
@@ -14153,7 +14153,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="140">
-        <f>SUM(D7:D13)</f>
+        <f>SUM(D8:D13)</f>
         <v>0</v>
       </c>
       <c r="E14" s="140">
